--- a/data/trans_orig/P6715-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6715-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen sentido sus tareas del trabajo en 2012</t>
+          <t>Población según si tienen sentido sus tareas del trabajo en 2012 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,62 +731,62 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9247</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8157</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30946</t>
+          <t>31487</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25344</t>
+          <t>24461</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26826</t>
+          <t>26032</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49097</t>
+          <t>50571</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48429</t>
+          <t>48755</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76411</t>
+          <t>76388</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31308</t>
+          <t>31547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52588</t>
+          <t>53917</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83511</t>
+          <t>86187</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120512</t>
+          <t>120930</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165411</t>
+          <t>163518</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>195905</t>
+          <t>195865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90060</t>
+          <t>87999</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>115985</t>
+          <t>113693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>264292</t>
+          <t>263402</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>303338</t>
+          <t>302970</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,42%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,62 +1448,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2109</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5298</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5226</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19082</t>
+          <t>18961</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35851</t>
+          <t>36077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61766</t>
+          <t>63673</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>30447</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53814</t>
+          <t>55306</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71977</t>
+          <t>71267</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>108180</t>
+          <t>106955</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77124</t>
+          <t>79109</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114376</t>
+          <t>114116</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48445</t>
+          <t>49398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76482</t>
+          <t>76066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134966</t>
+          <t>134446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183379</t>
+          <t>179891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241736</t>
+          <t>240493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>282014</t>
+          <t>282029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>144296</t>
+          <t>142995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177808</t>
+          <t>175893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396043</t>
+          <t>398512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>450270</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,1%</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28946</t>
+          <t>28993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>53071</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23608</t>
+          <t>23831</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45597</t>
+          <t>46750</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58376</t>
+          <t>57179</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92788</t>
+          <t>91534</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>37072</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66012</t>
+          <t>64268</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36274</t>
+          <t>34876</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64086</t>
+          <t>62386</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79400</t>
+          <t>81689</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116885</t>
+          <t>119024</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207756</t>
+          <t>207781</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241606</t>
+          <t>241387</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109462</t>
+          <t>109364</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>139948</t>
+          <t>140321</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>327711</t>
+          <t>328291</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>374644</t>
+          <t>373577</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19465</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16019</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13391</t>
+          <t>13027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31336</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41226</t>
+          <t>41898</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>69336</t>
+          <t>71114</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37008</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63949</t>
+          <t>63964</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>87464</t>
+          <t>87061</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>127803</t>
+          <t>126621</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>89600</t>
+          <t>90155</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126320</t>
+          <t>125618</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50894</t>
+          <t>50082</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>79405</t>
+          <t>78943</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148256</t>
+          <t>149351</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192827</t>
+          <t>195044</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>223141</t>
+          <t>222553</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>264206</t>
+          <t>263930</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>155691</t>
+          <t>154946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>189717</t>
+          <t>190840</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>388476</t>
+          <t>391060</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>442830</t>
+          <t>445314</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>62,08%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14569</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33731</t>
+          <t>34146</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32131</t>
+          <t>32411</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31570</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t>57400</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>140828</t>
+          <t>140832</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>190083</t>
+          <t>187550</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>120821</t>
+          <t>119466</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>165256</t>
+          <t>165605</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>271669</t>
+          <t>270698</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>336278</t>
+          <t>338308</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>280558</t>
+          <t>282577</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>346860</t>
+          <t>346216</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>188506</t>
+          <t>190680</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>242265</t>
+          <t>245139</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>483928</t>
+          <t>490877</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>565719</t>
+          <t>568812</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>877969</t>
+          <t>878206</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>951783</t>
+          <t>949987</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>528804</t>
+          <t>524803</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>592315</t>
+          <t>591828</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1429012</t>
+          <t>1428185</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1531251</t>
+          <t>1523844</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen sentido sus tareas del trabajo en 2016</t>
+          <t>Población según si tienen sentido sus tareas del trabajo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16752</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15498</t>
+          <t>16366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29678</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>25941</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48621</t>
+          <t>48378</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>34531</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45301</t>
+          <t>46612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75496</t>
+          <t>76582</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57889</t>
+          <t>58382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86893</t>
+          <t>88262</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46172</t>
+          <t>45627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68819</t>
+          <t>69603</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110782</t>
+          <t>111274</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148182</t>
+          <t>149634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105703</t>
+          <t>104982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136801</t>
+          <t>135829</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63255</t>
+          <t>64499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88337</t>
+          <t>88863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>176863</t>
+          <t>177438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217398</t>
+          <t>216527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14988</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24764</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>11942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11214</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30492</t>
+          <t>29366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34433</t>
+          <t>35262</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62188</t>
+          <t>63427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26893</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48419</t>
+          <t>47813</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67831</t>
+          <t>66963</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>102054</t>
+          <t>103758</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97140</t>
+          <t>96291</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134468</t>
+          <t>134319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69496</t>
+          <t>69725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99000</t>
+          <t>101652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>175477</t>
+          <t>177793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>222753</t>
+          <t>224403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211429</t>
+          <t>210115</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>253309</t>
+          <t>250767</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>131641</t>
+          <t>130733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163541</t>
+          <t>163540</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>348954</t>
+          <t>349839</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>404856</t>
+          <t>404634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,83%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11941</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25231</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36614</t>
+          <t>36216</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28091</t>
+          <t>27543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32271</t>
+          <t>31857</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58717</t>
+          <t>56296</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75140</t>
+          <t>74819</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110500</t>
+          <t>109454</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>49981</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77643</t>
+          <t>76759</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>130924</t>
+          <t>132545</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176841</t>
+          <t>176680</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87101</t>
+          <t>87910</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123160</t>
+          <t>122782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59659</t>
+          <t>60248</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90220</t>
+          <t>91119</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>156269</t>
+          <t>157001</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>203269</t>
+          <t>201804</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113794</t>
+          <t>113411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151063</t>
+          <t>151487</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92063</t>
+          <t>92171</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>124751</t>
+          <t>124548</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,47 +6239,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t>34,07%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>46,03%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>240364</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>215883</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>266639</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>37,89%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>34,03%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>46,11%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>240364</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>213304</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>265298</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>37,89%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>33,62%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19096</t>
+          <t>19918</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19195</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27383</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53066</t>
+          <t>53225</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25460</t>
+          <t>24699</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48043</t>
+          <t>47769</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58900</t>
+          <t>60674</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>92993</t>
+          <t>94724</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>91655</t>
+          <t>93078</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128303</t>
+          <t>127279</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58278</t>
+          <t>58950</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88709</t>
+          <t>88251</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>159805</t>
+          <t>159471</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>209313</t>
+          <t>206885</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>224954</t>
+          <t>222276</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>264636</t>
+          <t>261766</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>186440</t>
+          <t>186092</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>221904</t>
+          <t>220956</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>421473</t>
+          <t>420149</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>474544</t>
+          <t>474241</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,26%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26256</t>
+          <t>25272</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54204</t>
+          <t>54310</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>40101</t>
+          <t>41488</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>71694</t>
+          <t>71835</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26195</t>
+          <t>25640</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49142</t>
+          <t>49270</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>73917</t>
+          <t>73620</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>115847</t>
+          <t>109854</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>187394</t>
+          <t>185269</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>245956</t>
+          <t>243199</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>136914</t>
+          <t>138073</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>184754</t>
+          <t>184299</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>338013</t>
+          <t>336138</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>408699</t>
+          <t>408330</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>365035</t>
+          <t>370270</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>439389</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>259519</t>
+          <t>261970</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>316957</t>
+          <t>321751</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>643117</t>
+          <t>646749</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>735226</t>
+          <t>739985</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>689035</t>
+          <t>687163</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>765355</t>
+          <t>763921</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>507967</t>
+          <t>501356</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>571463</t>
+          <t>564509</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1213632</t>
+          <t>1209858</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1310511</t>
+          <t>1312738</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6715-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6715-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13804</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31487</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24461</t>
+          <t>24432</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>27007</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50571</t>
+          <t>49197</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48755</t>
+          <t>49718</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76388</t>
+          <t>75855</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31547</t>
+          <t>30690</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53917</t>
+          <t>53334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86187</t>
+          <t>85885</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120930</t>
+          <t>121652</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>163518</t>
+          <t>165092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>195865</t>
+          <t>195200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87999</t>
+          <t>89374</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113693</t>
+          <t>114721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>263402</t>
+          <t>261260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>302970</t>
+          <t>300581</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>69,87%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11939</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18961</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36077</t>
+          <t>36197</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63673</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>30110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55306</t>
+          <t>54491</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71267</t>
+          <t>71838</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106955</t>
+          <t>106578</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79109</t>
+          <t>77102</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114116</t>
+          <t>113945</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49398</t>
+          <t>49246</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76066</t>
+          <t>77597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134446</t>
+          <t>137552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179891</t>
+          <t>181105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>240493</t>
+          <t>242194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>282029</t>
+          <t>282050</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142995</t>
+          <t>144234</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175893</t>
+          <t>177801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398512</t>
+          <t>396621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>450123</t>
+          <t>446831</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,61%</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>17461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>28368</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53071</t>
+          <t>54891</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>23673</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46750</t>
+          <t>47235</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>57179</t>
+          <t>57378</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91534</t>
+          <t>92396</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37072</t>
+          <t>37296</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64268</t>
+          <t>64448</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34876</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62386</t>
+          <t>62561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81689</t>
+          <t>80591</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119024</t>
+          <t>119314</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207781</t>
+          <t>208456</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241387</t>
+          <t>243990</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109364</t>
+          <t>109025</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140321</t>
+          <t>141265</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>328291</t>
+          <t>326003</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>373577</t>
+          <t>374054</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16627</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30728</t>
+          <t>30338</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41898</t>
+          <t>42219</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71114</t>
+          <t>70649</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38304</t>
+          <t>38267</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63964</t>
+          <t>64523</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>87061</t>
+          <t>87467</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>126621</t>
+          <t>125566</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>90155</t>
+          <t>88656</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125618</t>
+          <t>124072</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50082</t>
+          <t>50343</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78943</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>149351</t>
+          <t>148120</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195044</t>
+          <t>194777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>222553</t>
+          <t>226177</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>263930</t>
+          <t>264765</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>154946</t>
+          <t>154212</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>190840</t>
+          <t>188915</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>391060</t>
+          <t>388977</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>445314</t>
+          <t>444787</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,01%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,77 +3479,77 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>6176</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>13422</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>12425</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>7044</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>21531</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>6176</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2871</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>12849</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>12425</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>6761</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>20739</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>33757</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>32308</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57400</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>140832</t>
+          <t>140876</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>187550</t>
+          <t>189782</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>119466</t>
+          <t>118568</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>165605</t>
+          <t>165440</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>270698</t>
+          <t>271083</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>338308</t>
+          <t>337885</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282577</t>
+          <t>282984</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>346216</t>
+          <t>347676</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>190680</t>
+          <t>188304</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>245139</t>
+          <t>245949</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>490877</t>
+          <t>487004</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>568812</t>
+          <t>571375</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>878206</t>
+          <t>878454</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>949987</t>
+          <t>951657</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>524803</t>
+          <t>528088</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>591828</t>
+          <t>591976</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1428185</t>
+          <t>1424726</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1523844</t>
+          <t>1524689</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>16300</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27969</t>
+          <t>27948</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25941</t>
+          <t>25829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48378</t>
+          <t>48583</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34531</t>
+          <t>34814</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46612</t>
+          <t>46832</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76582</t>
+          <t>75478</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58382</t>
+          <t>57913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88262</t>
+          <t>87168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45627</t>
+          <t>45558</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69603</t>
+          <t>68349</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111274</t>
+          <t>111614</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149634</t>
+          <t>148796</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104982</t>
+          <t>106666</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>135829</t>
+          <t>138880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64499</t>
+          <t>64538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88863</t>
+          <t>87882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177438</t>
+          <t>178779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>216527</t>
+          <t>217801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14261</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>23781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11942</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,47 +5218,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>19000</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>11675</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>30017</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>4,36%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>19000</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>11003</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>29366</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35262</t>
+          <t>34675</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>62257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25969</t>
+          <t>25930</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47813</t>
+          <t>47865</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66963</t>
+          <t>66119</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103758</t>
+          <t>101478</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96291</t>
+          <t>98148</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134319</t>
+          <t>135421</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69725</t>
+          <t>70320</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101652</t>
+          <t>98195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>177793</t>
+          <t>177020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>224403</t>
+          <t>224530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>210115</t>
+          <t>209709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>250767</t>
+          <t>250340</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130733</t>
+          <t>132751</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163540</t>
+          <t>164119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>349839</t>
+          <t>351693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>404634</t>
+          <t>406961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18754</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>25215</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>16682</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36216</t>
+          <t>38231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>28714</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31857</t>
+          <t>32939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56296</t>
+          <t>59353</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74819</t>
+          <t>76305</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109454</t>
+          <t>113073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49981</t>
+          <t>51838</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76759</t>
+          <t>79434</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>132545</t>
+          <t>134517</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176680</t>
+          <t>178570</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87910</t>
+          <t>87968</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>122782</t>
+          <t>124481</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60248</t>
+          <t>59372</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91119</t>
+          <t>90743</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>157001</t>
+          <t>155505</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>201804</t>
+          <t>204445</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113411</t>
+          <t>113901</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151487</t>
+          <t>151780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92171</t>
+          <t>90664</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>124548</t>
+          <t>124074</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>215883</t>
+          <t>213009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>266639</t>
+          <t>265018</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16059</t>
+          <t>15966</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19918</t>
+          <t>19897</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18720</t>
+          <t>18559</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29147</t>
+          <t>27616</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53225</t>
+          <t>53017</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24699</t>
+          <t>25129</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47769</t>
+          <t>48076</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>60674</t>
+          <t>59289</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>94724</t>
+          <t>91029</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93078</t>
+          <t>92385</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127279</t>
+          <t>127657</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58950</t>
+          <t>58609</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88251</t>
+          <t>90055</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>159471</t>
+          <t>158808</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>206885</t>
+          <t>205182</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>222276</t>
+          <t>224588</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>261766</t>
+          <t>262516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>186092</t>
+          <t>187117</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>220956</t>
+          <t>221726</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>420149</t>
+          <t>422079</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>474241</t>
+          <t>474424</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,29%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35524</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,49 +7116,49 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>16260</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>25899</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>16260</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>9272</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>25272</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>37</t>
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28081</t>
+          <t>28011</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54310</t>
+          <t>53802</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41488</t>
+          <t>41094</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>71835</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25640</t>
+          <t>25335</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49270</t>
+          <t>49680</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>73620</t>
+          <t>72782</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>113345</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>185269</t>
+          <t>186250</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>243199</t>
+          <t>244042</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>138073</t>
+          <t>137120</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>184299</t>
+          <t>184029</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>336138</t>
+          <t>339761</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>408330</t>
+          <t>414218</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>370270</t>
+          <t>367716</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>438466</t>
+          <t>436226</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,49 +7455,49 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>30,67%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>288412</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>262100</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>319738</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>27,81%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>25,27%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
           <t>30,83%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>288412</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>261970</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>321751</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>27,81%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>25,26%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>31,02%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>668</t>
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>646749</t>
+          <t>645287</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>739985</t>
+          <t>735483</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>687163</t>
+          <t>690276</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>763921</t>
+          <t>766886</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>501356</t>
+          <t>504407</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>564509</t>
+          <t>570991</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1209858</t>
+          <t>1212019</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1312738</t>
+          <t>1312523</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
